--- a/downloads/forms/shift-schedule.xlsx
+++ b/downloads/forms/shift-schedule.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="근무표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="근무표(주간)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'근무표'!$A$1:$K$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'근무표(주간)'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
